--- a/data/stx_xlsx/CATE.ST.xlsx
+++ b/data/stx_xlsx/CATE.ST.xlsx
@@ -9525,7 +9525,9 @@
       <c r="R25" s="16">
         <v>82.99</v>
       </c>
-      <c r="S25" s="20"/>
+      <c r="S25" s="16">
+        <v>40.15</v>
+      </c>
       <c r="T25" s="16">
         <v>29.82</v>
       </c>
@@ -10116,13 +10118,34 @@
         <v>1.04</v>
       </c>
       <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
+      <c r="P39" s="16">
+        <f t="shared" ref="P39:V39" si="1">SUM(P40:P41)</f>
+        <v>0.01</v>
+      </c>
+      <c r="Q39" s="16">
+        <f t="shared" si="1"/>
+        <v>1.18</v>
+      </c>
+      <c r="R39" s="16">
+        <f t="shared" si="1"/>
+        <v>1.58</v>
+      </c>
+      <c r="S39" s="16">
+        <f t="shared" si="1"/>
+        <v>2.23</v>
+      </c>
+      <c r="T39" s="16">
+        <f t="shared" si="1"/>
+        <v>2.92</v>
+      </c>
+      <c r="U39" s="16">
+        <f t="shared" si="1"/>
+        <v>3.76</v>
+      </c>
+      <c r="V39" s="16">
+        <f t="shared" si="1"/>
+        <v>1.79</v>
+      </c>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">

--- a/data/stx_xlsx/CATE.ST.xlsx
+++ b/data/stx_xlsx/CATE.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="389">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -237,31 +237,37 @@
     <t>Property expenses</t>
   </si>
   <si>
+    <t>Operating Expenses (not use)</t>
+  </si>
+  <si>
+    <t>Repairs and maintenance</t>
+  </si>
+  <si>
+    <t>Property maintenance and technical inspection</t>
+  </si>
+  <si>
+    <t>Property Tax (not use)</t>
+  </si>
+  <si>
+    <t>Other External Expenses</t>
+  </si>
+  <si>
+    <t>Property administration (not use)</t>
+  </si>
+  <si>
+    <t>Cost of revenues/COGS</t>
+  </si>
+  <si>
+    <t>Net operating surplus</t>
+  </si>
+  <si>
     <t>Operating Expenses</t>
   </si>
   <si>
-    <t>Repairs and maintenance</t>
-  </si>
-  <si>
-    <t>Property maintenance and technical inspection</t>
+    <t>Administration Cost</t>
   </si>
   <si>
     <t>Property Tax</t>
-  </si>
-  <si>
-    <t>Other External Expenses</t>
-  </si>
-  <si>
-    <t>Property administration</t>
-  </si>
-  <si>
-    <t>Cost of revenues/COGS</t>
-  </si>
-  <si>
-    <t>Net operating surplus</t>
-  </si>
-  <si>
-    <t>Administration Cost</t>
   </si>
   <si>
     <t>Other operating expenses</t>
@@ -1311,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1374,6 +1380,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2444,7 +2453,7 @@
       <c r="V22" s="20"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="21" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="20"/>
@@ -2600,7 +2609,7 @@
       <c r="V25" s="20"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="21" t="s">
         <v>75</v>
       </c>
       <c r="B26" s="20"/>
@@ -2704,7 +2713,7 @@
       <c r="V27" s="20"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="21" t="s">
         <v>77</v>
       </c>
       <c r="B28" s="20"/>
@@ -2801,13 +2810,13 @@
       <c r="O29" s="19">
         <v>87.06</v>
       </c>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="17" t="s">
@@ -2855,17 +2864,17 @@
       <c r="O30" s="18">
         <v>158.91</v>
       </c>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -2905,7 +2914,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -2945,7 +2954,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -2985,7 +2994,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -3031,75 +3040,75 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="22">
+        <v>84</v>
+      </c>
+      <c r="B35" s="23">
         <v>-15.89</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <v>-5.08</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <v>-6.97</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>-1.9</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>-6.01</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>-3.79</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="23">
         <v>-4.19</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="23">
         <v>-2.34</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="23">
         <v>-1.65</v>
       </c>
-      <c r="K35" s="22">
+      <c r="K35" s="23">
         <v>-10.11</v>
       </c>
-      <c r="L35" s="22">
+      <c r="L35" s="23">
         <v>-22.09</v>
       </c>
-      <c r="M35" s="22">
+      <c r="M35" s="23">
         <v>-8.82</v>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="23">
         <v>-1.9</v>
       </c>
-      <c r="O35" s="22">
+      <c r="O35" s="23">
         <v>-1.63</v>
       </c>
-      <c r="P35" s="22">
+      <c r="P35" s="23">
         <v>-0.08</v>
       </c>
-      <c r="Q35" s="22">
+      <c r="Q35" s="23">
         <v>-0.2</v>
       </c>
-      <c r="R35" s="22">
+      <c r="R35" s="23">
         <v>-0.21</v>
       </c>
-      <c r="S35" s="22">
+      <c r="S35" s="23">
         <v>-4.2</v>
       </c>
-      <c r="T35" s="22">
+      <c r="T35" s="23">
         <v>-5.55</v>
       </c>
-      <c r="U35" s="22">
+      <c r="U35" s="23">
         <v>-6.89</v>
       </c>
-      <c r="V35" s="22">
+      <c r="V35" s="23">
         <v>-19.7</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -3115,10 +3124,10 @@
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
       <c r="O36" s="20"/>
-      <c r="P36" s="22">
+      <c r="P36" s="23">
         <v>-74.89</v>
       </c>
-      <c r="Q36" s="23">
+      <c r="Q36" s="24">
         <v>-109.18</v>
       </c>
       <c r="R36" s="16">
@@ -3127,17 +3136,17 @@
       <c r="S36" s="15">
         <v>222.58</v>
       </c>
-      <c r="T36" s="23">
+      <c r="T36" s="24">
         <v>-145.01</v>
       </c>
-      <c r="U36" s="23">
+      <c r="U36" s="24">
         <v>-210.45</v>
       </c>
       <c r="V36" s="20"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" s="16">
         <v>7.41</v>
@@ -3145,7 +3154,7 @@
       <c r="C37" s="16">
         <v>31.53</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <v>-38.82</v>
       </c>
       <c r="E37" s="20">
@@ -3160,25 +3169,25 @@
       <c r="H37" s="16">
         <v>10.7</v>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="23">
         <v>-8.05</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37" s="23">
         <v>-8.04</v>
       </c>
       <c r="K37" s="16">
         <v>5.89</v>
       </c>
-      <c r="L37" s="22">
+      <c r="L37" s="23">
         <v>-11.86</v>
       </c>
-      <c r="M37" s="22">
+      <c r="M37" s="23">
         <v>-0.73</v>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="23">
         <v>-4.15</v>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="23">
         <v>-43.4</v>
       </c>
       <c r="P37" s="20"/>
@@ -3191,7 +3200,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -3231,7 +3240,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -3269,48 +3278,48 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="22">
+        <v>89</v>
+      </c>
+      <c r="B40" s="23">
         <v>-28.6</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <v>-57.97</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="23">
         <v>-34.83</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="23">
         <v>-31.35</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="23">
         <v>-7.52</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="23">
         <v>-2.15</v>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="23">
         <v>-3.16</v>
       </c>
-      <c r="I40" s="22">
+      <c r="I40" s="23">
         <v>-2.72</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40" s="23">
         <v>-3.97</v>
       </c>
-      <c r="K40" s="22">
+      <c r="K40" s="23">
         <v>-17.28</v>
       </c>
-      <c r="L40" s="22">
+      <c r="L40" s="23">
         <v>-6.88</v>
       </c>
-      <c r="M40" s="22">
+      <c r="M40" s="23">
         <v>-0.83</v>
       </c>
-      <c r="N40" s="22">
+      <c r="N40" s="23">
         <v>-16.61</v>
       </c>
-      <c r="O40" s="22">
+      <c r="O40" s="23">
         <v>-17.27</v>
       </c>
       <c r="P40" s="20"/>
@@ -3323,34 +3332,34 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="22">
+      <c r="C41" s="23">
         <v>-57.97</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <v>-32.84</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <v>-17.1</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="23">
         <v>-4.31</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <v>-2.15</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="23">
         <v>-2.23</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="23">
         <v>-2.72</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41" s="23">
         <v>-3.97</v>
       </c>
-      <c r="K41" s="22">
+      <c r="K41" s="23">
         <v>-8.44</v>
       </c>
       <c r="L41" s="20"/>
@@ -3367,30 +3376,30 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20">
         <v>0.0</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="23">
         <v>-1.99</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>-14.25</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="23">
         <v>-3.21</v>
       </c>
       <c r="G42" s="20">
         <v>0.0</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="23">
         <v>-0.93</v>
       </c>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
-      <c r="K42" s="22">
+      <c r="K42" s="23">
         <v>-8.84</v>
       </c>
       <c r="L42" s="20"/>
@@ -3407,7 +3416,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B43" s="15">
         <v>587.84</v>
@@ -3461,13 +3470,13 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B44" s="20"/>
-      <c r="C44" s="23">
+      <c r="C44" s="24">
         <v>-159.67</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <v>-131.38</v>
       </c>
       <c r="E44" s="16">
@@ -3493,7 +3502,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -3531,7 +3540,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="15">
@@ -3583,7 +3592,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="16">
@@ -3635,7 +3644,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B48" s="16">
         <v>8.47</v>
@@ -3675,7 +3684,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -3709,7 +3718,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -3728,10 +3737,10 @@
       <c r="P50" s="20"/>
       <c r="Q50" s="20"/>
       <c r="R50" s="20"/>
-      <c r="S50" s="22">
+      <c r="S50" s="23">
         <v>-3.64</v>
       </c>
-      <c r="T50" s="22">
+      <c r="T50" s="23">
         <v>-32.69</v>
       </c>
       <c r="U50" s="20"/>
@@ -3739,7 +3748,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -3755,10 +3764,10 @@
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
       <c r="O51" s="20"/>
-      <c r="P51" s="24">
+      <c r="P51" s="25">
         <v>9.26</v>
       </c>
-      <c r="Q51" s="24">
+      <c r="Q51" s="25">
         <v>8.7</v>
       </c>
       <c r="R51" s="16">
@@ -3771,7 +3780,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B52" s="16">
         <v>60.37</v>
@@ -3839,7 +3848,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="16">
@@ -3897,7 +3906,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="16">
@@ -3951,7 +3960,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="16">
@@ -4001,7 +4010,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B56" s="18">
         <v>619.61</v>
@@ -4045,10 +4054,10 @@
       <c r="O56" s="19">
         <v>5.24</v>
       </c>
-      <c r="P56" s="25">
+      <c r="P56" s="26">
         <v>-58.33</v>
       </c>
-      <c r="Q56" s="25">
+      <c r="Q56" s="26">
         <v>-92.58</v>
       </c>
       <c r="R56" s="19">
@@ -4057,10 +4066,10 @@
       <c r="S56" s="18">
         <v>257.18</v>
       </c>
-      <c r="T56" s="26">
+      <c r="T56" s="27">
         <v>-143.19</v>
       </c>
-      <c r="U56" s="26">
+      <c r="U56" s="27">
         <v>-169.23</v>
       </c>
       <c r="V56" s="19">
@@ -4069,7 +4078,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B57" s="18">
         <v>1708.43</v>
@@ -4122,7 +4131,7 @@
       <c r="R57" s="19">
         <v>4.94</v>
       </c>
-      <c r="S57" s="25">
+      <c r="S57" s="26">
         <v>-95.28</v>
       </c>
       <c r="T57" s="18">
@@ -4137,9 +4146,9 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B58" s="22">
+        <v>107</v>
+      </c>
+      <c r="B58" s="23">
         <v>-3.18</v>
       </c>
       <c r="C58" s="16">
@@ -4172,7 +4181,7 @@
       <c r="L58" s="16">
         <v>97.71</v>
       </c>
-      <c r="M58" s="22">
+      <c r="M58" s="23">
         <v>-5.97</v>
       </c>
       <c r="N58" s="16">
@@ -4191,7 +4200,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B59" s="15">
         <v>513.69</v>
@@ -4245,7 +4254,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -4285,7 +4294,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -4311,25 +4320,25 @@
       <c r="S61" s="16">
         <v>28.62</v>
       </c>
-      <c r="T61" s="22">
+      <c r="T61" s="23">
         <v>-0.95</v>
       </c>
-      <c r="U61" s="22">
+      <c r="U61" s="23">
         <v>-9.57</v>
       </c>
       <c r="V61" s="20"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B62" s="22">
+        <v>111</v>
+      </c>
+      <c r="B62" s="23">
         <v>-29.66</v>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <v>-48.82</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="24">
         <v>-294.6</v>
       </c>
       <c r="E62" s="15">
@@ -4350,13 +4359,13 @@
       <c r="J62" s="16">
         <v>24.98</v>
       </c>
-      <c r="K62" s="22">
+      <c r="K62" s="23">
         <v>-37.9</v>
       </c>
       <c r="L62" s="16">
         <v>29.16</v>
       </c>
-      <c r="M62" s="23">
+      <c r="M62" s="24">
         <v>-138.34</v>
       </c>
       <c r="N62" s="16">
@@ -4373,7 +4382,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -4389,31 +4398,31 @@
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
       <c r="O63" s="20"/>
-      <c r="P63" s="22">
+      <c r="P63" s="23">
         <v>-14.83</v>
       </c>
-      <c r="Q63" s="22">
+      <c r="Q63" s="23">
         <v>-23.7</v>
       </c>
-      <c r="R63" s="22">
+      <c r="R63" s="23">
         <v>-28.84</v>
       </c>
-      <c r="S63" s="22">
+      <c r="S63" s="23">
         <v>-52.17</v>
       </c>
-      <c r="T63" s="22">
+      <c r="T63" s="23">
         <v>-46.77</v>
       </c>
-      <c r="U63" s="22">
+      <c r="U63" s="23">
         <v>-39.16</v>
       </c>
-      <c r="V63" s="22">
+      <c r="V63" s="23">
         <v>-6.28</v>
       </c>
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -4425,10 +4434,10 @@
       <c r="I64" s="20">
         <v>0.0</v>
       </c>
-      <c r="J64" s="22">
+      <c r="J64" s="23">
         <v>-82.02</v>
       </c>
-      <c r="K64" s="22">
+      <c r="K64" s="23">
         <v>-38.2</v>
       </c>
       <c r="L64" s="20"/>
@@ -4445,7 +4454,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -4471,7 +4480,7 @@
       <c r="S65" s="16">
         <v>0.04</v>
       </c>
-      <c r="T65" s="22">
+      <c r="T65" s="23">
         <v>-12.61</v>
       </c>
       <c r="U65" s="16">
@@ -4483,7 +4492,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -4501,7 +4510,7 @@
       <c r="O66" s="20"/>
       <c r="P66" s="20"/>
       <c r="Q66" s="20"/>
-      <c r="R66" s="22">
+      <c r="R66" s="23">
         <v>-1.37</v>
       </c>
       <c r="S66" s="20"/>
@@ -4511,7 +4520,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -4535,13 +4544,13 @@
       <c r="U67" s="20">
         <v>0.0</v>
       </c>
-      <c r="V67" s="22">
+      <c r="V67" s="23">
         <v>-0.28</v>
       </c>
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -4565,13 +4574,13 @@
       <c r="U68" s="20">
         <v>0.0</v>
       </c>
-      <c r="V68" s="22">
+      <c r="V68" s="23">
         <v>-0.04</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B69" s="18">
         <v>480.86</v>
@@ -4615,31 +4624,31 @@
       <c r="O69" s="19">
         <v>45.98</v>
       </c>
-      <c r="P69" s="25">
+      <c r="P69" s="26">
         <v>-3.27</v>
       </c>
-      <c r="Q69" s="25">
+      <c r="Q69" s="26">
         <v>-7.82</v>
       </c>
-      <c r="R69" s="25">
+      <c r="R69" s="26">
         <v>-28.86</v>
       </c>
-      <c r="S69" s="25">
+      <c r="S69" s="26">
         <v>-18.71</v>
       </c>
-      <c r="T69" s="25">
+      <c r="T69" s="26">
         <v>-58.25</v>
       </c>
-      <c r="U69" s="25">
+      <c r="U69" s="26">
         <v>-35.77</v>
       </c>
-      <c r="V69" s="25">
+      <c r="V69" s="26">
         <v>-1.86</v>
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -4658,7 +4667,7 @@
       <c r="P70" s="20"/>
       <c r="Q70" s="20"/>
       <c r="R70" s="20"/>
-      <c r="S70" s="22">
+      <c r="S70" s="23">
         <v>-57.25</v>
       </c>
       <c r="T70" s="16">
@@ -4671,7 +4680,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B71" s="18">
         <v>2189.29</v>
@@ -4721,10 +4730,10 @@
       <c r="Q71" s="18">
         <v>107.79</v>
       </c>
-      <c r="R71" s="25">
+      <c r="R71" s="26">
         <v>-23.92</v>
       </c>
-      <c r="S71" s="26">
+      <c r="S71" s="27">
         <v>-171.24</v>
       </c>
       <c r="T71" s="18">
@@ -4733,13 +4742,13 @@
       <c r="U71" s="18">
         <v>306.57</v>
       </c>
-      <c r="V71" s="25">
+      <c r="V71" s="26">
         <v>-0.71</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B72" s="15">
         <v>448.03</v>
@@ -4773,10 +4782,10 @@
       <c r="Q72" s="16">
         <v>29.36</v>
       </c>
-      <c r="R72" s="22">
+      <c r="R72" s="23">
         <v>-6.33</v>
       </c>
-      <c r="S72" s="22">
+      <c r="S72" s="23">
         <v>-58.38</v>
       </c>
       <c r="T72" s="16">
@@ -4785,13 +4794,13 @@
       <c r="U72" s="16">
         <v>84.66</v>
       </c>
-      <c r="V72" s="22">
+      <c r="V72" s="23">
         <v>-5.07</v>
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="16">
@@ -4843,7 +4852,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="15">
@@ -4891,10 +4900,10 @@
       <c r="Q74" s="16">
         <v>28.09</v>
       </c>
-      <c r="R74" s="22">
+      <c r="R74" s="23">
         <v>-7.1</v>
       </c>
-      <c r="S74" s="22">
+      <c r="S74" s="23">
         <v>-59.52</v>
       </c>
       <c r="T74" s="16">
@@ -4903,13 +4912,13 @@
       <c r="U74" s="16">
         <v>67.9</v>
       </c>
-      <c r="V74" s="22">
+      <c r="V74" s="23">
         <v>-2.1</v>
       </c>
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -4931,7 +4940,7 @@
       <c r="Q75" s="16">
         <v>3.93</v>
       </c>
-      <c r="R75" s="22">
+      <c r="R75" s="23">
         <v>-0.66</v>
       </c>
       <c r="S75" s="16">
@@ -4943,13 +4952,13 @@
       <c r="U75" s="16">
         <v>16.76</v>
       </c>
-      <c r="V75" s="22">
+      <c r="V75" s="23">
         <v>-2.98</v>
       </c>
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -4971,7 +4980,7 @@
       <c r="Q76" s="16">
         <v>3.93</v>
       </c>
-      <c r="R76" s="22">
+      <c r="R76" s="23">
         <v>-0.66</v>
       </c>
       <c r="S76" s="16">
@@ -4983,13 +4992,13 @@
       <c r="U76" s="16">
         <v>16.34</v>
       </c>
-      <c r="V76" s="22">
+      <c r="V76" s="23">
         <v>-3.23</v>
       </c>
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -5023,7 +5032,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -5051,7 +5060,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -5068,7 +5077,7 @@
       <c r="N79" s="20"/>
       <c r="O79" s="20"/>
       <c r="P79" s="20"/>
-      <c r="Q79" s="22">
+      <c r="Q79" s="23">
         <v>-2.66</v>
       </c>
       <c r="R79" s="16">
@@ -5081,7 +5090,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B80" s="18">
         <v>448.03</v>
@@ -5131,10 +5140,10 @@
       <c r="Q80" s="19">
         <v>29.36</v>
       </c>
-      <c r="R80" s="25">
+      <c r="R80" s="26">
         <v>-6.33</v>
       </c>
-      <c r="S80" s="25">
+      <c r="S80" s="26">
         <v>-58.38</v>
       </c>
       <c r="T80" s="19">
@@ -5143,13 +5152,13 @@
       <c r="U80" s="19">
         <v>84.66</v>
       </c>
-      <c r="V80" s="25">
+      <c r="V80" s="26">
         <v>-5.07</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B81" s="18">
         <v>1741.26</v>
@@ -5199,10 +5208,10 @@
       <c r="Q81" s="19">
         <v>78.43</v>
       </c>
-      <c r="R81" s="25">
+      <c r="R81" s="26">
         <v>-17.59</v>
       </c>
-      <c r="S81" s="26">
+      <c r="S81" s="27">
         <v>-112.86</v>
       </c>
       <c r="T81" s="18">
@@ -5217,7 +5226,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B82" s="18">
         <v>1741.26</v>
@@ -5267,10 +5276,10 @@
       <c r="Q82" s="19">
         <v>78.43</v>
       </c>
-      <c r="R82" s="25">
+      <c r="R82" s="26">
         <v>-17.59</v>
       </c>
-      <c r="S82" s="26">
+      <c r="S82" s="27">
         <v>-112.86</v>
       </c>
       <c r="T82" s="18">
@@ -5285,7 +5294,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -5317,22 +5326,22 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
-      <c r="K84" s="21"/>
-      <c r="L84" s="21"/>
-      <c r="M84" s="21"/>
-      <c r="N84" s="21"/>
-      <c r="O84" s="21"/>
+        <v>131</v>
+      </c>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
       <c r="P84" s="19">
         <v>59.25</v>
       </c>
@@ -5342,14 +5351,14 @@
       <c r="R84" s="18">
         <v>115.27</v>
       </c>
-      <c r="S84" s="21"/>
-      <c r="T84" s="21"/>
-      <c r="U84" s="21"/>
-      <c r="V84" s="21"/>
+      <c r="S84" s="22"/>
+      <c r="T84" s="22"/>
+      <c r="U84" s="22"/>
+      <c r="V84" s="22"/>
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20">
@@ -5368,13 +5377,13 @@
       <c r="L85" s="20">
         <v>0.0</v>
       </c>
-      <c r="M85" s="22">
+      <c r="M85" s="23">
         <v>-0.55</v>
       </c>
-      <c r="N85" s="22">
+      <c r="N85" s="23">
         <v>-1.62</v>
       </c>
-      <c r="O85" s="22">
+      <c r="O85" s="23">
         <v>-2.06</v>
       </c>
       <c r="P85" s="20"/>
@@ -5387,45 +5396,45 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21">
+        <v>133</v>
+      </c>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22">
         <v>0.0</v>
       </c>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21">
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="22"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="22">
         <v>0.0</v>
       </c>
-      <c r="L86" s="21">
+      <c r="L86" s="22">
         <v>0.0</v>
       </c>
-      <c r="M86" s="25">
+      <c r="M86" s="26">
         <v>-0.55</v>
       </c>
-      <c r="N86" s="25">
+      <c r="N86" s="26">
         <v>-1.62</v>
       </c>
-      <c r="O86" s="25">
+      <c r="O86" s="26">
         <v>-2.06</v>
       </c>
-      <c r="P86" s="21"/>
-      <c r="Q86" s="21"/>
-      <c r="R86" s="21"/>
-      <c r="S86" s="21"/>
-      <c r="T86" s="21"/>
-      <c r="U86" s="21"/>
-      <c r="V86" s="21"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="T86" s="22"/>
+      <c r="U86" s="22"/>
+      <c r="V86" s="22"/>
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B87" s="18">
         <v>1741.26</v>
@@ -5478,7 +5487,7 @@
       <c r="R87" s="19">
         <v>97.68</v>
       </c>
-      <c r="S87" s="26">
+      <c r="S87" s="27">
         <v>-112.86</v>
       </c>
       <c r="T87" s="18">
@@ -5493,7 +5502,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B88" s="18">
         <v>1741.26</v>
@@ -5543,10 +5552,10 @@
       <c r="Q88" s="19">
         <v>78.43</v>
       </c>
-      <c r="R88" s="25">
+      <c r="R88" s="26">
         <v>-17.59</v>
       </c>
-      <c r="S88" s="26">
+      <c r="S88" s="27">
         <v>-112.86</v>
       </c>
       <c r="T88" s="18">
@@ -5561,7 +5570,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B89" s="18">
         <v>1741.26</v>
@@ -5614,7 +5623,7 @@
       <c r="R89" s="19">
         <v>97.68</v>
       </c>
-      <c r="S89" s="26">
+      <c r="S89" s="27">
         <v>-112.86</v>
       </c>
       <c r="T89" s="18">
@@ -5629,7 +5638,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="15">
@@ -5671,7 +5680,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="16">
@@ -5686,7 +5695,7 @@
       <c r="F91" s="16">
         <v>11.53</v>
       </c>
-      <c r="G91" s="22">
+      <c r="G91" s="23">
         <v>-9.93</v>
       </c>
       <c r="H91" s="16">
@@ -5713,9 +5722,9 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B92" s="21"/>
+        <v>139</v>
+      </c>
+      <c r="B92" s="22"/>
       <c r="C92" s="19">
         <v>20.34</v>
       </c>
@@ -5728,7 +5737,7 @@
       <c r="F92" s="19">
         <v>11.53</v>
       </c>
-      <c r="G92" s="25">
+      <c r="G92" s="26">
         <v>-9.93</v>
       </c>
       <c r="H92" s="19">
@@ -5740,22 +5749,22 @@
       <c r="J92" s="19">
         <v>4.07</v>
       </c>
-      <c r="K92" s="21"/>
-      <c r="L92" s="21"/>
-      <c r="M92" s="21"/>
-      <c r="N92" s="21"/>
-      <c r="O92" s="21"/>
-      <c r="P92" s="21"/>
-      <c r="Q92" s="21"/>
-      <c r="R92" s="21"/>
-      <c r="S92" s="21"/>
-      <c r="T92" s="21"/>
-      <c r="U92" s="21"/>
-      <c r="V92" s="21"/>
+      <c r="K92" s="22"/>
+      <c r="L92" s="22"/>
+      <c r="M92" s="22"/>
+      <c r="N92" s="22"/>
+      <c r="O92" s="22"/>
+      <c r="P92" s="22"/>
+      <c r="Q92" s="22"/>
+      <c r="R92" s="22"/>
+      <c r="S92" s="22"/>
+      <c r="T92" s="22"/>
+      <c r="U92" s="22"/>
+      <c r="V92" s="22"/>
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20">
@@ -5797,7 +5806,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="15">
@@ -5839,9 +5848,9 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B95" s="21"/>
+        <v>142</v>
+      </c>
+      <c r="B95" s="22"/>
       <c r="C95" s="18">
         <v>1118.7</v>
       </c>
@@ -5866,22 +5875,22 @@
       <c r="J95" s="18">
         <v>618.68</v>
       </c>
-      <c r="K95" s="21"/>
-      <c r="L95" s="21"/>
-      <c r="M95" s="21"/>
-      <c r="N95" s="21"/>
-      <c r="O95" s="21"/>
-      <c r="P95" s="21"/>
-      <c r="Q95" s="21"/>
-      <c r="R95" s="21"/>
-      <c r="S95" s="21"/>
-      <c r="T95" s="21"/>
-      <c r="U95" s="21"/>
-      <c r="V95" s="21"/>
+      <c r="K95" s="22"/>
+      <c r="L95" s="22"/>
+      <c r="M95" s="22"/>
+      <c r="N95" s="22"/>
+      <c r="O95" s="22"/>
+      <c r="P95" s="22"/>
+      <c r="Q95" s="22"/>
+      <c r="R95" s="22"/>
+      <c r="S95" s="22"/>
+      <c r="T95" s="22"/>
+      <c r="U95" s="22"/>
+      <c r="V95" s="22"/>
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B96" s="16">
         <v>60.4</v>
@@ -5949,7 +5958,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B97" s="16">
         <v>60.4</v>
@@ -6017,7 +6026,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B98" s="16">
         <v>28.85</v>
@@ -6070,7 +6079,7 @@
       <c r="R98" s="16">
         <v>8.44</v>
       </c>
-      <c r="S98" s="22">
+      <c r="S98" s="23">
         <v>-9.76</v>
       </c>
       <c r="T98" s="16">
@@ -6085,7 +6094,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B99" s="16">
         <v>28.85</v>
@@ -6135,10 +6144,10 @@
       <c r="Q99" s="16">
         <v>6.78</v>
       </c>
-      <c r="R99" s="22">
+      <c r="R99" s="23">
         <v>-1.52</v>
       </c>
-      <c r="S99" s="22">
+      <c r="S99" s="23">
         <v>-9.76</v>
       </c>
       <c r="T99" s="16">
@@ -6153,7 +6162,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B100" s="16">
         <v>28.85</v>
@@ -6206,7 +6215,7 @@
       <c r="R100" s="16">
         <v>8.44</v>
       </c>
-      <c r="S100" s="22">
+      <c r="S100" s="23">
         <v>-9.76</v>
       </c>
       <c r="T100" s="16">
@@ -6221,7 +6230,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B101" s="16">
         <v>28.85</v>
@@ -6271,10 +6280,10 @@
       <c r="Q101" s="16">
         <v>6.78</v>
       </c>
-      <c r="R101" s="22">
+      <c r="R101" s="23">
         <v>-1.52</v>
       </c>
-      <c r="S101" s="22">
+      <c r="S101" s="23">
         <v>-9.76</v>
       </c>
       <c r="T101" s="16">
@@ -6289,7 +6298,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B102" s="15">
         <v>1741.26</v>
@@ -6342,7 +6351,7 @@
       <c r="R102" s="16">
         <v>97.68</v>
       </c>
-      <c r="S102" s="23">
+      <c r="S102" s="24">
         <v>-112.86</v>
       </c>
       <c r="T102" s="15">
@@ -6357,7 +6366,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -6391,7 +6400,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B104" s="15">
         <v>472.27</v>
@@ -6429,7 +6438,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -6469,7 +6478,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="16">
@@ -6507,7 +6516,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B107" s="16">
         <v>8.47</v>
@@ -6545,7 +6554,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="16">
@@ -6581,7 +6590,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="16">
@@ -6643,7 +6652,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="16">
@@ -6705,7 +6714,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="16">
@@ -6755,7 +6764,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="16">
@@ -6811,7 +6820,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="16">
@@ -6867,7 +6876,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -6915,7 +6924,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="16">
@@ -6979,7 +6988,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -7009,7 +7018,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B117" s="15">
         <v>1741.26</v>
@@ -7059,10 +7068,10 @@
       <c r="Q117" s="16">
         <v>78.43</v>
       </c>
-      <c r="R117" s="22">
+      <c r="R117" s="23">
         <v>-17.59</v>
       </c>
-      <c r="S117" s="23">
+      <c r="S117" s="24">
         <v>-112.86</v>
       </c>
       <c r="T117" s="15">
@@ -7077,7 +7086,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -7105,14 +7114,14 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="20"/>
-      <c r="G119" s="22">
+      <c r="G119" s="23">
         <v>-8.19</v>
       </c>
       <c r="H119" s="20"/>
@@ -7133,7 +7142,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B120" s="16">
         <v>28.85</v>
@@ -7187,7 +7196,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B121" s="16">
         <v>28.85</v>
@@ -7241,7 +7250,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B122" s="16">
         <v>28.85</v>
@@ -7295,7 +7304,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B123" s="16">
         <v>28.85</v>
@@ -7349,7 +7358,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B124" s="16">
         <v>60.4</v>
@@ -7403,7 +7412,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B125" s="16">
         <v>60.4</v>
@@ -7457,7 +7466,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B126" s="15">
         <v>1741.26</v>
@@ -7511,7 +7520,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B127" s="16">
         <v>1.0</v>
@@ -7565,7 +7574,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B128" s="16">
         <v>1.0</v>
@@ -7619,7 +7628,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B129" s="15">
         <v>1741.26</v>
@@ -7673,7 +7682,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B130" s="15">
         <v>1741.26</v>
@@ -7727,7 +7736,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B131" s="15">
         <v>1741.26</v>
@@ -8670,7 +8679,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9043,67 +9052,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -9134,7 +9143,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -9228,7 +9237,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="16">
@@ -9294,7 +9303,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="15">
@@ -9360,7 +9369,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="16">
@@ -9402,7 +9411,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="16">
@@ -9444,7 +9453,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -9472,7 +9481,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B25" s="15">
         <v>485.5</v>
@@ -9540,7 +9549,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -9580,7 +9589,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -9610,7 +9619,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B28" s="15">
         <v>510.65</v>
@@ -9646,7 +9655,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="15">
@@ -9680,7 +9689,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="16">
@@ -9714,7 +9723,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="16">
@@ -9748,7 +9757,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20">
@@ -9778,7 +9787,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -9836,7 +9845,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -9864,7 +9873,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -9894,7 +9903,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B36" s="18">
         <v>996.15</v>
@@ -9962,7 +9971,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B37" s="15">
         <v>636.4</v>
@@ -10008,7 +10017,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B38" s="20">
         <v>48629.74</v>
@@ -10076,7 +10085,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B39" s="20">
         <v>0.0</v>
@@ -10149,7 +10158,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="16">
@@ -10213,71 +10222,71 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="22">
+      <c r="C41" s="23">
         <v>-8.22</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <v>-7.05</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <v>-5.65</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="23">
         <v>-4.87</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <v>-4.7</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="23">
         <v>-3.75</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="23">
         <v>-3.42</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41" s="23">
         <v>-2.6</v>
       </c>
-      <c r="K41" s="22">
+      <c r="K41" s="23">
         <v>-1.71</v>
       </c>
-      <c r="L41" s="22">
+      <c r="L41" s="23">
         <v>-1.05</v>
       </c>
-      <c r="M41" s="22">
+      <c r="M41" s="23">
         <v>-0.48</v>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="23">
         <v>-0.09</v>
       </c>
       <c r="O41" s="20"/>
-      <c r="P41" s="22">
+      <c r="P41" s="23">
         <v>-1.95</v>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41" s="23">
         <v>-2.49</v>
       </c>
-      <c r="R41" s="22">
+      <c r="R41" s="23">
         <v>-1.77</v>
       </c>
-      <c r="S41" s="22">
+      <c r="S41" s="23">
         <v>-3.63</v>
       </c>
-      <c r="T41" s="22">
+      <c r="T41" s="23">
         <v>-2.59</v>
       </c>
-      <c r="U41" s="22">
+      <c r="U41" s="23">
         <v>-1.72</v>
       </c>
-      <c r="V41" s="22">
+      <c r="V41" s="23">
         <v>-1.05</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -10311,7 +10320,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B43" s="15">
         <v>301.8</v>
@@ -10351,7 +10360,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B44" s="15">
         <v>607.97</v>
@@ -10387,7 +10396,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="15">
@@ -10439,7 +10448,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -10471,7 +10480,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="15">
@@ -10527,7 +10536,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -10575,36 +10584,36 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B49" s="21">
+        <v>209</v>
+      </c>
+      <c r="B49" s="22">
         <v>50175.91</v>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="22">
         <v>44262.6</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="22">
         <v>32651.39</v>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="22">
         <v>27001.13</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="22">
         <v>23885.42</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="22">
         <v>20569.19</v>
       </c>
-      <c r="H49" s="21">
+      <c r="H49" s="22">
         <v>16280.45</v>
       </c>
-      <c r="I49" s="21">
+      <c r="I49" s="22">
         <v>15039.07</v>
       </c>
-      <c r="J49" s="21">
+      <c r="J49" s="22">
         <v>14022.96</v>
       </c>
-      <c r="K49" s="21">
+      <c r="K49" s="22">
         <v>11025.15</v>
       </c>
       <c r="L49" s="18">
@@ -10643,36 +10652,36 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B50" s="21">
+        <v>210</v>
+      </c>
+      <c r="B50" s="22">
         <v>51172.05</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="22">
         <v>45838.67</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="22">
         <v>33725.61</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="22">
         <v>29373.12</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="22">
         <v>25156.85</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="22">
         <v>21300.23</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="22">
         <v>16662.36</v>
       </c>
-      <c r="I50" s="21">
+      <c r="I50" s="22">
         <v>15521.93</v>
       </c>
-      <c r="J50" s="21">
+      <c r="J50" s="22">
         <v>14255.81</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="22">
         <v>11706.9</v>
       </c>
       <c r="L50" s="18">
@@ -10711,7 +10720,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B51" s="15">
         <v>2832.08</v>
@@ -10777,7 +10786,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="15">
@@ -10843,7 +10852,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B53" s="15">
         <v>1225.78</v>
@@ -10889,7 +10898,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -10931,7 +10940,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -10979,7 +10988,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="15">
@@ -11045,7 +11054,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="15">
@@ -11091,7 +11100,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="16">
@@ -11137,7 +11146,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="16">
@@ -11183,7 +11192,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="16">
@@ -11229,7 +11238,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -11267,7 +11276,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="15">
@@ -11325,7 +11334,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -11361,7 +11370,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -11382,7 +11391,7 @@
       <c r="N64" s="20"/>
       <c r="O64" s="20"/>
       <c r="P64" s="20"/>
-      <c r="Q64" s="22">
+      <c r="Q64" s="23">
         <v>-26.03</v>
       </c>
       <c r="R64" s="20"/>
@@ -11393,7 +11402,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -11429,7 +11438,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -11457,7 +11466,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -11487,7 +11496,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -11517,7 +11526,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B69" s="18">
         <v>4057.85</v>
@@ -11585,7 +11594,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B70" s="20">
         <v>16601.01</v>
@@ -11627,7 +11636,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B71" s="15">
         <v>3998.81</v>
@@ -11681,7 +11690,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B72" s="15">
         <v>300.7</v>
@@ -11723,7 +11732,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B73" s="16">
         <v>1.09</v>
@@ -11789,7 +11798,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -11841,7 +11850,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -11881,7 +11890,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -11921,7 +11930,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -11961,7 +11970,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -11991,21 +12000,21 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="21">
+        <v>237</v>
+      </c>
+      <c r="B79" s="22">
         <v>20901.62</v>
       </c>
-      <c r="C79" s="21">
+      <c r="C79" s="22">
         <v>20562.94</v>
       </c>
-      <c r="D79" s="21">
+      <c r="D79" s="22">
         <v>12720.47</v>
       </c>
-      <c r="E79" s="21">
+      <c r="E79" s="22">
         <v>10236.26</v>
       </c>
-      <c r="F79" s="21">
+      <c r="F79" s="22">
         <v>11959.27</v>
       </c>
       <c r="G79" s="18">
@@ -12059,30 +12068,30 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B80" s="21">
+        <v>238</v>
+      </c>
+      <c r="B80" s="22">
         <v>24959.47</v>
       </c>
-      <c r="C80" s="21">
+      <c r="C80" s="22">
         <v>22090.69</v>
       </c>
-      <c r="D80" s="21">
+      <c r="D80" s="22">
         <v>16216.97</v>
       </c>
-      <c r="E80" s="21">
+      <c r="E80" s="22">
         <v>13656.82</v>
       </c>
-      <c r="F80" s="21">
+      <c r="F80" s="22">
         <v>14191.34</v>
       </c>
-      <c r="G80" s="21">
+      <c r="G80" s="22">
         <v>13374.33</v>
       </c>
-      <c r="H80" s="21">
+      <c r="H80" s="22">
         <v>10738.21</v>
       </c>
-      <c r="I80" s="21">
+      <c r="I80" s="22">
         <v>10341.28</v>
       </c>
       <c r="J80" s="18">
@@ -12127,7 +12136,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="15">
@@ -12193,7 +12202,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="20">
@@ -12259,7 +12268,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20">
@@ -12319,13 +12328,13 @@
       <c r="U83" s="15">
         <v>206.55</v>
       </c>
-      <c r="V83" s="22">
+      <c r="V83" s="23">
         <v>-23.17</v>
       </c>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="16">
@@ -12359,7 +12368,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -12376,42 +12385,42 @@
       <c r="N85" s="20"/>
       <c r="O85" s="20"/>
       <c r="P85" s="20"/>
-      <c r="Q85" s="22">
+      <c r="Q85" s="23">
         <v>-6.48</v>
       </c>
       <c r="R85" s="16">
         <v>7.92</v>
       </c>
-      <c r="S85" s="22">
+      <c r="S85" s="23">
         <v>-7.81</v>
       </c>
-      <c r="T85" s="22">
+      <c r="T85" s="23">
         <v>-1.47</v>
       </c>
-      <c r="U85" s="22">
+      <c r="U85" s="23">
         <v>-21.3</v>
       </c>
-      <c r="V85" s="22">
+      <c r="V85" s="23">
         <v>-3.21</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="B86" s="21">
+        <v>244</v>
+      </c>
+      <c r="B86" s="22">
         <v>26212.58</v>
       </c>
-      <c r="C86" s="21">
+      <c r="C86" s="22">
         <v>23747.98</v>
       </c>
-      <c r="D86" s="21">
+      <c r="D86" s="22">
         <v>17508.64</v>
       </c>
-      <c r="E86" s="21">
+      <c r="E86" s="22">
         <v>15716.31</v>
       </c>
-      <c r="F86" s="21">
+      <c r="F86" s="22">
         <v>10965.51</v>
       </c>
       <c r="G86" s="18">
@@ -12465,7 +12474,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20">
@@ -12517,31 +12526,31 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21">
+        <v>245</v>
+      </c>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22">
         <v>0.0</v>
       </c>
-      <c r="D88" s="21">
+      <c r="D88" s="22">
         <v>0.0</v>
       </c>
-      <c r="E88" s="21">
+      <c r="E88" s="22">
         <v>0.0</v>
       </c>
-      <c r="F88" s="21">
+      <c r="F88" s="22">
         <v>0.0</v>
       </c>
-      <c r="G88" s="21">
+      <c r="G88" s="22">
         <v>0.0</v>
       </c>
-      <c r="H88" s="21">
+      <c r="H88" s="22">
         <v>0.0</v>
       </c>
-      <c r="I88" s="21">
+      <c r="I88" s="22">
         <v>0.0</v>
       </c>
-      <c r="J88" s="21">
+      <c r="J88" s="22">
         <v>0.0</v>
       </c>
       <c r="K88" s="19">
@@ -12559,31 +12568,31 @@
       <c r="O88" s="19">
         <v>6.25</v>
       </c>
-      <c r="P88" s="21"/>
-      <c r="Q88" s="21"/>
-      <c r="R88" s="21"/>
-      <c r="S88" s="21"/>
-      <c r="T88" s="21"/>
-      <c r="U88" s="21"/>
-      <c r="V88" s="21"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="T88" s="22"/>
+      <c r="U88" s="22"/>
+      <c r="V88" s="22"/>
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="B89" s="21">
+        <v>246</v>
+      </c>
+      <c r="B89" s="22">
         <v>26212.58</v>
       </c>
-      <c r="C89" s="21">
+      <c r="C89" s="22">
         <v>23747.98</v>
       </c>
-      <c r="D89" s="21">
+      <c r="D89" s="22">
         <v>17508.64</v>
       </c>
-      <c r="E89" s="21">
+      <c r="E89" s="22">
         <v>15716.31</v>
       </c>
-      <c r="F89" s="21">
+      <c r="F89" s="22">
         <v>10965.51</v>
       </c>
       <c r="G89" s="18">
@@ -12637,36 +12646,36 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="B90" s="21">
+        <v>247</v>
+      </c>
+      <c r="B90" s="22">
         <v>51172.05</v>
       </c>
-      <c r="C90" s="21">
+      <c r="C90" s="22">
         <v>45838.67</v>
       </c>
-      <c r="D90" s="21">
+      <c r="D90" s="22">
         <v>33725.61</v>
       </c>
-      <c r="E90" s="21">
+      <c r="E90" s="22">
         <v>29373.12</v>
       </c>
-      <c r="F90" s="21">
+      <c r="F90" s="22">
         <v>25156.85</v>
       </c>
-      <c r="G90" s="21">
+      <c r="G90" s="22">
         <v>21300.23</v>
       </c>
-      <c r="H90" s="21">
+      <c r="H90" s="22">
         <v>16662.36</v>
       </c>
-      <c r="I90" s="21">
+      <c r="I90" s="22">
         <v>15521.93</v>
       </c>
-      <c r="J90" s="21">
+      <c r="J90" s="22">
         <v>14255.81</v>
       </c>
-      <c r="K90" s="21">
+      <c r="K90" s="22">
         <v>11706.9</v>
       </c>
       <c r="L90" s="18">
@@ -12705,7 +12714,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B91" s="16">
         <v>60.36</v>
@@ -12773,7 +12782,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B92" s="16">
         <v>60.36</v>
@@ -12841,7 +12850,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B93" s="20">
         <v>0.0</v>
@@ -12909,7 +12918,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B94" s="15">
         <v>487.57</v>
@@ -12949,7 +12958,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -12983,7 +12992,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -13041,7 +13050,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -13069,7 +13078,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -13101,7 +13110,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -13133,7 +13142,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -13163,7 +13172,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20">
@@ -13223,7 +13232,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="15">
@@ -13283,7 +13292,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="15">
@@ -13343,7 +13352,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="15">
@@ -13387,7 +13396,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="15">
@@ -13421,7 +13430,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="15">
@@ -13471,7 +13480,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -13499,7 +13508,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="15">
@@ -13535,7 +13544,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -13573,7 +13582,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -13590,28 +13599,28 @@
       <c r="N110" s="20"/>
       <c r="O110" s="20"/>
       <c r="P110" s="20"/>
-      <c r="Q110" s="22">
+      <c r="Q110" s="23">
         <v>-0.05</v>
       </c>
-      <c r="R110" s="22">
+      <c r="R110" s="23">
         <v>-0.05</v>
       </c>
-      <c r="S110" s="22">
+      <c r="S110" s="23">
         <v>-0.11</v>
       </c>
-      <c r="T110" s="22">
+      <c r="T110" s="23">
         <v>-0.11</v>
       </c>
-      <c r="U110" s="22">
+      <c r="U110" s="23">
         <v>-0.07</v>
       </c>
-      <c r="V110" s="22">
+      <c r="V110" s="23">
         <v>-0.08</v>
       </c>
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="15">
@@ -13649,7 +13658,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="16">
@@ -13699,7 +13708,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="16">
@@ -13749,7 +13758,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B114" s="16">
         <v>60.36</v>
@@ -13817,7 +13826,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B115" s="16">
         <v>60.36</v>
@@ -13885,7 +13894,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B116" s="20">
         <v>0.0</v>
@@ -13953,7 +13962,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B117" s="16">
         <v>1.0</v>
@@ -14021,7 +14030,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -14059,7 +14068,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -14097,7 +14106,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -14125,7 +14134,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B121" s="16">
         <v>74.0</v>
@@ -14193,7 +14202,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20">
@@ -14221,7 +14230,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -14273,7 +14282,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -14325,7 +14334,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -14377,7 +14386,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -14429,7 +14438,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="20">
@@ -15388,7 +15397,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15761,67 +15770,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15894,7 +15903,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15988,71 +15997,71 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="B20" s="22">
+        <v>288</v>
+      </c>
+      <c r="B20" s="23">
         <v>-75.2</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <v>-37.63</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <v>-38.82</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="23">
         <v>-42.76</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="23">
         <v>-19.84</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <v>-14.12</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <v>-14.05</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="23">
         <v>-12.83</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="23">
         <v>-2.81</v>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="23">
         <v>-1.57</v>
       </c>
-      <c r="L20" s="22">
+      <c r="L20" s="23">
         <v>-0.48</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
-      <c r="O20" s="22">
+      <c r="O20" s="23">
         <v>-0.26</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="23">
         <v>-4.29</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="23">
         <v>-3.93</v>
       </c>
       <c r="R20" s="16">
         <v>11.77</v>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="23">
         <v>-1.14</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="23">
         <v>-22.5</v>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="23">
         <v>-11.89</v>
       </c>
-      <c r="V20" s="22">
+      <c r="V20" s="23">
         <v>-3.16</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -16068,7 +16077,7 @@
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
       <c r="O21" s="20"/>
-      <c r="P21" s="22">
+      <c r="P21" s="23">
         <v>-14.83</v>
       </c>
       <c r="Q21" s="20"/>
@@ -16080,7 +16089,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B22" s="15">
         <v>1640.64</v>
@@ -16130,7 +16139,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B23" s="15">
         <v>2189.29</v>
@@ -16180,7 +16189,7 @@
       <c r="Q23" s="15">
         <v>107.69</v>
       </c>
-      <c r="R23" s="22">
+      <c r="R23" s="23">
         <v>-23.92</v>
       </c>
       <c r="S23" s="16">
@@ -16192,48 +16201,48 @@
       <c r="U23" s="16">
         <v>86.56</v>
       </c>
-      <c r="V23" s="22">
+      <c r="V23" s="23">
         <v>-0.71</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B24" s="23">
+        <v>292</v>
+      </c>
+      <c r="B24" s="24">
         <v>-473.45</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <v>-52.88</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
         <v>-265.74</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <v>-1436.62</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="24">
         <v>-2547.31</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="24">
         <v>-1225.11</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="24">
         <v>-832.78</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="24">
         <v>-351.74</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="24">
         <v>-326.33</v>
       </c>
-      <c r="K24" s="22">
+      <c r="K24" s="23">
         <v>-89.06</v>
       </c>
-      <c r="L24" s="23">
+      <c r="L24" s="24">
         <v>-333.01</v>
       </c>
-      <c r="M24" s="23">
+      <c r="M24" s="24">
         <v>-216.33</v>
       </c>
       <c r="N24" s="20"/>
@@ -16243,32 +16252,32 @@
       </c>
       <c r="Q24" s="20"/>
       <c r="R24" s="20"/>
-      <c r="S24" s="22">
+      <c r="S24" s="23">
         <v>-0.14</v>
       </c>
       <c r="T24" s="16">
         <v>10.7</v>
       </c>
-      <c r="U24" s="22">
+      <c r="U24" s="23">
         <v>-0.6</v>
       </c>
       <c r="V24" s="20"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B25" s="20"/>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <v>-1.02</v>
       </c>
       <c r="D25" s="20">
         <v>0.0</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <v>-2.85</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="23">
         <v>-3.31</v>
       </c>
       <c r="G25" s="16">
@@ -16284,10 +16293,10 @@
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
       <c r="O25" s="20"/>
-      <c r="P25" s="22">
+      <c r="P25" s="23">
         <v>-78.42</v>
       </c>
-      <c r="Q25" s="23">
+      <c r="Q25" s="24">
         <v>-119.21</v>
       </c>
       <c r="R25" s="16">
@@ -16302,7 +16311,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="16">
@@ -16352,46 +16361,46 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B27" s="20"/>
-      <c r="C27" s="23">
+      <c r="C27" s="24">
         <v>-115.94</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
         <v>-521.52</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <v>-726.86</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="24">
         <v>-2323.22</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="24">
         <v>-1186.01</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="24">
         <v>-736.28</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="24">
         <v>-308.19</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="24">
         <v>-281.89</v>
       </c>
-      <c r="K27" s="22">
+      <c r="K27" s="23">
         <v>-37.61</v>
       </c>
-      <c r="L27" s="23">
+      <c r="L27" s="24">
         <v>-189.6</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="24">
         <v>-360.54</v>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="23">
         <v>-27.89</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="23">
         <v>-22.34</v>
       </c>
       <c r="P27" s="20"/>
@@ -16404,7 +16413,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -16434,7 +16443,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="16">
@@ -16443,35 +16452,35 @@
       <c r="D29" s="15">
         <v>293.61</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <v>-612.84</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="24">
         <v>-202.95</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="23">
         <v>-38.99</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="23">
         <v>-27.27</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="23">
         <v>-32.78</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29" s="23">
         <v>-24.98</v>
       </c>
       <c r="K29" s="16">
         <v>37.81</v>
       </c>
-      <c r="L29" s="22">
+      <c r="L29" s="23">
         <v>-29.16</v>
       </c>
       <c r="M29" s="15">
         <v>138.34</v>
       </c>
       <c r="N29" s="20"/>
-      <c r="O29" s="22">
+      <c r="O29" s="23">
         <v>-23.29</v>
       </c>
       <c r="P29" s="20"/>
@@ -16484,13 +16493,13 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="16">
         <v>31.53</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <v>-38.82</v>
       </c>
       <c r="E30" s="20">
@@ -16505,25 +16514,25 @@
       <c r="H30" s="16">
         <v>10.7</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="23">
         <v>-8.05</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="23">
         <v>-8.04</v>
       </c>
       <c r="K30" s="16">
         <v>5.89</v>
       </c>
-      <c r="L30" s="22">
+      <c r="L30" s="23">
         <v>-11.86</v>
       </c>
-      <c r="M30" s="22">
+      <c r="M30" s="23">
         <v>-0.55</v>
       </c>
-      <c r="N30" s="22">
+      <c r="N30" s="23">
         <v>-4.15</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="23">
         <v>-43.4</v>
       </c>
       <c r="P30" s="20"/>
@@ -16536,46 +16545,46 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B31" s="20"/>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <v>-17.29</v>
       </c>
       <c r="D31" s="20">
         <v>0.0</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>-95.01</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>-21.15</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>-7.27</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="23">
         <v>-69.33</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="23">
         <v>-3.28</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="23">
         <v>-65.85</v>
       </c>
-      <c r="K31" s="22">
+      <c r="K31" s="23">
         <v>-11.39</v>
       </c>
-      <c r="L31" s="22">
+      <c r="L31" s="23">
         <v>-96.85</v>
       </c>
-      <c r="M31" s="22">
+      <c r="M31" s="23">
         <v>-5.97</v>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="23">
         <v>-2.17</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="23">
         <v>-0.34</v>
       </c>
       <c r="P31" s="20"/>
@@ -16588,7 +16597,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -16596,19 +16605,19 @@
       <c r="E32" s="20"/>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="22">
+      <c r="H32" s="23">
         <v>-12.19</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="23">
         <v>-1.12</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="23">
         <v>-18.69</v>
       </c>
       <c r="K32" s="16">
         <v>1.77</v>
       </c>
-      <c r="L32" s="22">
+      <c r="L32" s="23">
         <v>-0.86</v>
       </c>
       <c r="M32" s="20"/>
@@ -16624,7 +16633,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -16637,13 +16646,13 @@
         <v>0.84</v>
       </c>
       <c r="J33" s="20"/>
-      <c r="K33" s="22">
+      <c r="K33" s="23">
         <v>-86.31</v>
       </c>
-      <c r="L33" s="22">
+      <c r="L33" s="23">
         <v>-5.16</v>
       </c>
-      <c r="M33" s="22">
+      <c r="M33" s="23">
         <v>-0.09</v>
       </c>
       <c r="N33" s="16">
@@ -16666,7 +16675,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -16676,7 +16685,7 @@
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
-      <c r="J34" s="22">
+      <c r="J34" s="23">
         <v>-1.94</v>
       </c>
       <c r="K34" s="20"/>
@@ -16696,7 +16705,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" s="16">
         <v>65.67</v>
@@ -16704,28 +16713,28 @@
       <c r="C35" s="16">
         <v>12.2</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <v>-31.85</v>
       </c>
       <c r="E35" s="15">
         <v>114.02</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>-15.53</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>-13.51</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="23">
         <v>-81.05</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="23">
         <v>-13.02</v>
       </c>
       <c r="J35" s="16">
         <v>25.37</v>
       </c>
-      <c r="K35" s="22">
+      <c r="K35" s="23">
         <v>-97.21</v>
       </c>
       <c r="L35" s="16">
@@ -16737,10 +16746,10 @@
       <c r="N35" s="16">
         <v>3.52</v>
       </c>
-      <c r="O35" s="22">
+      <c r="O35" s="23">
         <v>-13.24</v>
       </c>
-      <c r="P35" s="22">
+      <c r="P35" s="23">
         <v>-4.39</v>
       </c>
       <c r="Q35" s="16">
@@ -16764,9 +16773,9 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="B36" s="22">
+        <v>303</v>
+      </c>
+      <c r="B36" s="23">
         <v>-37.07</v>
       </c>
       <c r="C36" s="16">
@@ -16787,10 +16796,10 @@
       <c r="H36" s="16">
         <v>82.17</v>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="23">
         <v>-17.98</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36" s="23">
         <v>-39.7</v>
       </c>
       <c r="K36" s="16">
@@ -16799,40 +16808,40 @@
       <c r="L36" s="16">
         <v>28.21</v>
       </c>
-      <c r="M36" s="22">
+      <c r="M36" s="23">
         <v>-36.56</v>
       </c>
-      <c r="N36" s="22">
+      <c r="N36" s="23">
         <v>-8.84</v>
       </c>
-      <c r="O36" s="22">
+      <c r="O36" s="23">
         <v>-8.42</v>
       </c>
-      <c r="P36" s="22">
+      <c r="P36" s="23">
         <v>-23.94</v>
       </c>
-      <c r="Q36" s="22">
+      <c r="Q36" s="23">
         <v>-27.08</v>
       </c>
       <c r="R36" s="16">
         <v>27.93</v>
       </c>
-      <c r="S36" s="22">
+      <c r="S36" s="23">
         <v>-3.48</v>
       </c>
-      <c r="T36" s="22">
+      <c r="T36" s="23">
         <v>-57.09</v>
       </c>
       <c r="U36" s="15">
         <v>140.85</v>
       </c>
-      <c r="V36" s="23">
+      <c r="V36" s="24">
         <v>-276.61</v>
       </c>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -16862,7 +16871,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -16894,7 +16903,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -16919,14 +16928,14 @@
       <c r="T39" s="16">
         <v>0.02</v>
       </c>
-      <c r="U39" s="22">
+      <c r="U39" s="23">
         <v>-0.96</v>
       </c>
       <c r="V39" s="20"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B40" s="18">
         <v>1669.24</v>
@@ -16970,7 +16979,7 @@
       <c r="O40" s="19">
         <v>88.35</v>
       </c>
-      <c r="P40" s="25">
+      <c r="P40" s="26">
         <v>-32.68</v>
       </c>
       <c r="Q40" s="19">
@@ -16988,13 +16997,13 @@
       <c r="U40" s="18">
         <v>231.33</v>
       </c>
-      <c r="V40" s="25">
+      <c r="V40" s="26">
         <v>-0.85</v>
       </c>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
@@ -17036,9 +17045,9 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B42" s="23">
+        <v>307</v>
+      </c>
+      <c r="B42" s="24">
         <v>-664.1</v>
       </c>
       <c r="C42" s="20"/>
@@ -17047,23 +17056,23 @@
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
-      <c r="I42" s="22">
+      <c r="I42" s="23">
         <v>-70.52</v>
       </c>
-      <c r="J42" s="23">
+      <c r="J42" s="24">
         <v>-611.99</v>
       </c>
-      <c r="K42" s="23">
+      <c r="K42" s="24">
         <v>-812.86</v>
       </c>
-      <c r="L42" s="23">
+      <c r="L42" s="24">
         <v>-446.5</v>
       </c>
-      <c r="M42" s="23">
+      <c r="M42" s="24">
         <v>-157.35</v>
       </c>
       <c r="N42" s="20"/>
-      <c r="O42" s="22">
+      <c r="O42" s="23">
         <v>-95.22</v>
       </c>
       <c r="P42" s="20"/>
@@ -17076,7 +17085,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -17124,25 +17133,25 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B44" s="20"/>
-      <c r="C44" s="23">
+      <c r="C44" s="24">
         <v>-2028.91</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <v>-677.78</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <v>-1110.72</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="24">
         <v>-535.38</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="24">
         <v>-176.45</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="23">
         <v>-17.4</v>
       </c>
       <c r="I44" s="20"/>
@@ -17162,7 +17171,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20">
@@ -17192,7 +17201,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B46" s="16">
         <v>77.32</v>
@@ -17226,75 +17235,75 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B47" s="23">
+        <v>311</v>
+      </c>
+      <c r="B47" s="24">
         <v>-1220.16</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="24">
         <v>-2694.03</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="24">
         <v>-2010.46</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>-1480.33</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="24">
         <v>-1001.1</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="24">
         <v>-991.86</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="24">
         <v>-700.36</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="24">
         <v>-745.99</v>
       </c>
-      <c r="J47" s="23">
+      <c r="J47" s="24">
         <v>-503.83</v>
       </c>
-      <c r="K47" s="23">
+      <c r="K47" s="24">
         <v>-564.33</v>
       </c>
-      <c r="L47" s="23">
+      <c r="L47" s="24">
         <v>-136.34</v>
       </c>
-      <c r="M47" s="23">
+      <c r="M47" s="24">
         <v>-165.71</v>
       </c>
-      <c r="N47" s="23">
+      <c r="N47" s="24">
         <v>-242.69</v>
       </c>
-      <c r="O47" s="23">
+      <c r="O47" s="24">
         <v>-178.5</v>
       </c>
-      <c r="P47" s="22">
+      <c r="P47" s="23">
         <v>-2.84</v>
       </c>
-      <c r="Q47" s="22">
+      <c r="Q47" s="23">
         <v>-2.59</v>
       </c>
-      <c r="R47" s="22">
+      <c r="R47" s="23">
         <v>-0.44</v>
       </c>
-      <c r="S47" s="23">
+      <c r="S47" s="24">
         <v>-130.65</v>
       </c>
-      <c r="T47" s="23">
+      <c r="T47" s="24">
         <v>-104.45</v>
       </c>
-      <c r="U47" s="23">
+      <c r="U47" s="24">
         <v>-100.69</v>
       </c>
-      <c r="V47" s="22">
+      <c r="V47" s="23">
         <v>-6.93</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20">
@@ -17346,52 +17355,52 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>-1.99</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="23">
         <v>-0.95</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>-2.0</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="23">
         <v>-0.41</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="23">
         <v>-2.98</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49" s="23">
         <v>-0.37</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49" s="23">
         <v>-0.58</v>
       </c>
-      <c r="K49" s="22">
+      <c r="K49" s="23">
         <v>-0.39</v>
       </c>
-      <c r="L49" s="22">
+      <c r="L49" s="23">
         <v>-0.29</v>
       </c>
-      <c r="M49" s="22">
+      <c r="M49" s="23">
         <v>-1.65</v>
       </c>
-      <c r="N49" s="22">
+      <c r="N49" s="23">
         <v>-1.17</v>
       </c>
       <c r="O49" s="20"/>
       <c r="P49" s="20"/>
-      <c r="Q49" s="22">
+      <c r="Q49" s="23">
         <v>-0.13</v>
       </c>
-      <c r="R49" s="22">
+      <c r="R49" s="23">
         <v>-0.29</v>
       </c>
-      <c r="S49" s="22">
+      <c r="S49" s="23">
         <v>-0.2</v>
       </c>
       <c r="T49" s="20"/>
@@ -17400,7 +17409,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B50" s="16">
         <v>41.31</v>
@@ -17408,10 +17417,10 @@
       <c r="C50" s="20">
         <v>0.0</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="23">
         <v>-27.87</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="23">
         <v>-11.4</v>
       </c>
       <c r="F50" s="20"/>
@@ -17450,7 +17459,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -17470,7 +17479,7 @@
       <c r="Q51" s="15">
         <v>464.28</v>
       </c>
-      <c r="R51" s="22">
+      <c r="R51" s="23">
         <v>-29.34</v>
       </c>
       <c r="S51" s="20"/>
@@ -17480,35 +17489,35 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
-      <c r="F52" s="22">
+      <c r="F52" s="23">
         <v>-89.5</v>
       </c>
-      <c r="G52" s="22">
+      <c r="G52" s="23">
         <v>-16.99</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52" s="23">
         <v>-69.89</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52" s="23">
         <v>-86.16</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52" s="23">
         <v>-98.09</v>
       </c>
       <c r="K52" s="20"/>
-      <c r="L52" s="23">
+      <c r="L52" s="24">
         <v>-593.93</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="23">
         <v>-52.18</v>
       </c>
-      <c r="N52" s="23">
+      <c r="N52" s="24">
         <v>-383.75</v>
       </c>
       <c r="O52" s="20"/>
@@ -17522,7 +17531,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -17558,7 +17567,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -17570,7 +17579,7 @@
       <c r="I54" s="20">
         <v>0.0</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54" s="23">
         <v>-69.33</v>
       </c>
       <c r="K54" s="20"/>
@@ -17588,66 +17597,66 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B55" s="26">
+        <v>319</v>
+      </c>
+      <c r="B55" s="27">
         <v>-1765.62</v>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <v>-4490.04</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="27">
         <v>-2693.22</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="27">
         <v>-1855.63</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F55" s="27">
         <v>-1599.32</v>
       </c>
-      <c r="G55" s="26">
+      <c r="G55" s="27">
         <v>-1024.4</v>
       </c>
-      <c r="H55" s="26">
+      <c r="H55" s="27">
         <v>-768.2</v>
       </c>
-      <c r="I55" s="26">
+      <c r="I55" s="27">
         <v>-763.32</v>
       </c>
-      <c r="J55" s="26">
+      <c r="J55" s="27">
         <v>-785.81</v>
       </c>
-      <c r="K55" s="26">
+      <c r="K55" s="27">
         <v>-567.67</v>
       </c>
-      <c r="L55" s="26">
+      <c r="L55" s="27">
         <v>-415.33</v>
       </c>
-      <c r="M55" s="26">
+      <c r="M55" s="27">
         <v>-362.66</v>
       </c>
-      <c r="N55" s="26">
+      <c r="N55" s="27">
         <v>-367.42</v>
       </c>
-      <c r="O55" s="26">
+      <c r="O55" s="27">
         <v>-154.78</v>
       </c>
-      <c r="P55" s="25">
+      <c r="P55" s="26">
         <v>-1.86</v>
       </c>
       <c r="Q55" s="18">
         <v>461.57</v>
       </c>
-      <c r="R55" s="25">
+      <c r="R55" s="26">
         <v>-30.07</v>
       </c>
-      <c r="S55" s="26">
+      <c r="S55" s="27">
         <v>-127.2</v>
       </c>
       <c r="T55" s="19">
         <v>99.34</v>
       </c>
-      <c r="U55" s="25">
+      <c r="U55" s="26">
         <v>-98.64</v>
       </c>
       <c r="V55" s="19">
@@ -17656,7 +17665,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B56" s="20">
         <v>0.0</v>
@@ -17686,7 +17695,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B57" s="15">
         <v>102.74</v>
@@ -17730,83 +17739,83 @@
       <c r="O57" s="15">
         <v>284.73</v>
       </c>
-      <c r="P57" s="23">
+      <c r="P57" s="24">
         <v>-587.6</v>
       </c>
-      <c r="Q57" s="22">
+      <c r="Q57" s="23">
         <v>-4.2</v>
       </c>
-      <c r="R57" s="22">
+      <c r="R57" s="23">
         <v>-4.12</v>
       </c>
       <c r="S57" s="15">
         <v>111.04</v>
       </c>
-      <c r="T57" s="22">
+      <c r="T57" s="23">
         <v>-80.24</v>
       </c>
-      <c r="U57" s="23">
+      <c r="U57" s="24">
         <v>-129.68</v>
       </c>
       <c r="V57" s="20"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B58" s="23">
+        <v>322</v>
+      </c>
+      <c r="B58" s="24">
         <v>-575.13</v>
       </c>
-      <c r="C58" s="23">
+      <c r="C58" s="24">
         <v>-498.33</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="24">
         <v>-411.05</v>
       </c>
-      <c r="E58" s="23">
+      <c r="E58" s="24">
         <v>-344.9</v>
       </c>
-      <c r="F58" s="23">
+      <c r="F58" s="24">
         <v>-309.88</v>
       </c>
-      <c r="G58" s="23">
+      <c r="G58" s="24">
         <v>-250.75</v>
       </c>
-      <c r="H58" s="23">
+      <c r="H58" s="24">
         <v>-201.75</v>
       </c>
-      <c r="I58" s="23">
+      <c r="I58" s="24">
         <v>-157.7</v>
       </c>
-      <c r="J58" s="23">
+      <c r="J58" s="24">
         <v>-121.14</v>
       </c>
-      <c r="K58" s="22">
+      <c r="K58" s="23">
         <v>-97.9</v>
       </c>
-      <c r="L58" s="22">
+      <c r="L58" s="23">
         <v>-73.52</v>
       </c>
-      <c r="M58" s="22">
+      <c r="M58" s="23">
         <v>-47.12</v>
       </c>
       <c r="N58" s="20">
         <v>0.0</v>
       </c>
       <c r="O58" s="20"/>
-      <c r="P58" s="23">
+      <c r="P58" s="24">
         <v>-589.3</v>
       </c>
-      <c r="Q58" s="23">
+      <c r="Q58" s="24">
         <v>-308.36</v>
       </c>
-      <c r="R58" s="22">
+      <c r="R58" s="23">
         <v>-49.97</v>
       </c>
-      <c r="S58" s="22">
+      <c r="S58" s="23">
         <v>-51.93</v>
       </c>
-      <c r="T58" s="22">
+      <c r="T58" s="23">
         <v>-50.11</v>
       </c>
       <c r="U58" s="20"/>
@@ -17814,46 +17823,46 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B59" s="20"/>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <v>-13502.68</v>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="24">
         <v>-4691.73</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="24">
         <v>-4079.92</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="24">
         <v>-6036.79</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="24">
         <v>-6036.6</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="24">
         <v>-2368.34</v>
       </c>
-      <c r="I59" s="23">
+      <c r="I59" s="24">
         <v>-1658.58</v>
       </c>
-      <c r="J59" s="23">
+      <c r="J59" s="24">
         <v>-4889.76</v>
       </c>
-      <c r="K59" s="23">
+      <c r="K59" s="24">
         <v>-1892.52</v>
       </c>
-      <c r="L59" s="23">
+      <c r="L59" s="24">
         <v>-1345.43</v>
       </c>
-      <c r="M59" s="23">
+      <c r="M59" s="24">
         <v>-1078.97</v>
       </c>
-      <c r="N59" s="22">
+      <c r="N59" s="23">
         <v>-16.52</v>
       </c>
-      <c r="O59" s="23">
+      <c r="O59" s="24">
         <v>-218.21</v>
       </c>
       <c r="P59" s="20"/>
@@ -17866,7 +17875,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -17908,7 +17917,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -17925,10 +17934,10 @@
       <c r="N61" s="20"/>
       <c r="O61" s="20"/>
       <c r="P61" s="20"/>
-      <c r="Q61" s="23">
+      <c r="Q61" s="24">
         <v>-251.63</v>
       </c>
-      <c r="R61" s="22">
+      <c r="R61" s="23">
         <v>-2.54</v>
       </c>
       <c r="S61" s="20"/>
@@ -17938,15 +17947,15 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="B62" s="26">
+        <v>324</v>
+      </c>
+      <c r="B62" s="27">
         <v>-472.39</v>
       </c>
       <c r="C62" s="18">
         <v>3748.65</v>
       </c>
-      <c r="D62" s="25">
+      <c r="D62" s="26">
         <v>-91.57</v>
       </c>
       <c r="E62" s="18">
@@ -17982,29 +17991,29 @@
       <c r="O62" s="19">
         <v>66.52</v>
       </c>
-      <c r="P62" s="26">
+      <c r="P62" s="27">
         <v>-1176.91</v>
       </c>
-      <c r="Q62" s="26">
+      <c r="Q62" s="27">
         <v>-564.18</v>
       </c>
-      <c r="R62" s="25">
+      <c r="R62" s="26">
         <v>-56.62</v>
       </c>
       <c r="S62" s="19">
         <v>59.11</v>
       </c>
-      <c r="T62" s="26">
+      <c r="T62" s="27">
         <v>-130.35</v>
       </c>
-      <c r="U62" s="25">
+      <c r="U62" s="26">
         <v>-77.47</v>
       </c>
-      <c r="V62" s="21"/>
+      <c r="V62" s="22"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -18032,7 +18041,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -18060,43 +18069,43 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="21"/>
-      <c r="O65" s="21"/>
+        <v>327</v>
+      </c>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
       <c r="P65" s="18">
         <v>1243.94</v>
       </c>
-      <c r="Q65" s="21"/>
-      <c r="R65" s="21"/>
-      <c r="S65" s="21"/>
-      <c r="T65" s="21"/>
-      <c r="U65" s="21"/>
-      <c r="V65" s="21"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="22"/>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="22"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="B66" s="23">
+        <v>328</v>
+      </c>
+      <c r="B66" s="24">
         <v>-568.77</v>
       </c>
       <c r="C66" s="15">
         <v>567.48</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="24">
         <v>-1727.8</v>
       </c>
       <c r="E66" s="15">
@@ -18108,16 +18117,16 @@
       <c r="G66" s="15">
         <v>286.68</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="24">
         <v>-140.43</v>
       </c>
       <c r="I66" s="15">
         <v>174.28</v>
       </c>
-      <c r="J66" s="22">
+      <c r="J66" s="23">
         <v>-49.29</v>
       </c>
-      <c r="K66" s="22">
+      <c r="K66" s="23">
         <v>-55.09</v>
       </c>
       <c r="L66" s="20"/>
@@ -18134,7 +18143,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B67" s="15">
         <v>1082.53</v>
@@ -18202,24 +18211,24 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="B68" s="22">
+        <v>330</v>
+      </c>
+      <c r="B68" s="23">
         <v>-9.53</v>
       </c>
       <c r="C68" s="16">
         <v>2.03</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="23">
         <v>-1.0</v>
       </c>
       <c r="E68" s="16">
         <v>15.2</v>
       </c>
-      <c r="F68" s="22">
+      <c r="F68" s="23">
         <v>-0.4</v>
       </c>
-      <c r="G68" s="22">
+      <c r="G68" s="23">
         <v>-0.2</v>
       </c>
       <c r="H68" s="16">
@@ -18239,7 +18248,7 @@
       <c r="N68" s="20"/>
       <c r="O68" s="20"/>
       <c r="P68" s="20"/>
-      <c r="Q68" s="22">
+      <c r="Q68" s="23">
         <v>-0.42</v>
       </c>
       <c r="R68" s="16">
@@ -18252,7 +18261,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B69" s="15">
         <v>485.5</v>
@@ -18320,15 +18329,15 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="B70" s="26">
+        <v>332</v>
+      </c>
+      <c r="B70" s="27">
         <v>-578.3</v>
       </c>
       <c r="C70" s="18">
         <v>569.52</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="27">
         <v>-1728.8</v>
       </c>
       <c r="E70" s="18">
@@ -18340,22 +18349,22 @@
       <c r="G70" s="18">
         <v>286.47</v>
       </c>
-      <c r="H70" s="26">
+      <c r="H70" s="27">
         <v>-139.59</v>
       </c>
       <c r="I70" s="18">
         <v>174.56</v>
       </c>
-      <c r="J70" s="25">
+      <c r="J70" s="26">
         <v>-49.1</v>
       </c>
-      <c r="K70" s="25">
+      <c r="K70" s="26">
         <v>-54.99</v>
       </c>
       <c r="L70" s="19">
         <v>2.01</v>
       </c>
-      <c r="M70" s="25">
+      <c r="M70" s="26">
         <v>-13.04</v>
       </c>
       <c r="N70" s="18">
@@ -18367,7 +18376,7 @@
       <c r="P70" s="19">
         <v>32.5</v>
       </c>
-      <c r="Q70" s="25">
+      <c r="Q70" s="26">
         <v>-38.49</v>
       </c>
       <c r="R70" s="19">
@@ -18376,81 +18385,81 @@
       <c r="S70" s="19">
         <v>8.29</v>
       </c>
-      <c r="T70" s="25">
+      <c r="T70" s="26">
         <v>-24.28</v>
       </c>
       <c r="U70" s="19">
         <v>55.22</v>
       </c>
-      <c r="V70" s="21">
+      <c r="V70" s="22">
         <v>0.0</v>
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B71" s="20"/>
-      <c r="C71" s="23">
+      <c r="C71" s="24">
         <v>-554.26</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D71" s="24">
         <v>-390.15</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="24">
         <v>-226.13</v>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="24">
         <v>-241.53</v>
       </c>
-      <c r="G71" s="23">
+      <c r="G71" s="24">
         <v>-249.93</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="24">
         <v>-221.39</v>
       </c>
-      <c r="I71" s="23">
+      <c r="I71" s="24">
         <v>-216.61</v>
       </c>
-      <c r="J71" s="23">
+      <c r="J71" s="24">
         <v>-208.87</v>
       </c>
-      <c r="K71" s="23">
+      <c r="K71" s="24">
         <v>-199.44</v>
       </c>
-      <c r="L71" s="22">
+      <c r="L71" s="23">
         <v>-85.0</v>
       </c>
-      <c r="M71" s="22">
+      <c r="M71" s="23">
         <v>-82.86</v>
       </c>
-      <c r="N71" s="22">
+      <c r="N71" s="23">
         <v>-69.67</v>
       </c>
-      <c r="O71" s="22">
+      <c r="O71" s="23">
         <v>-64.54</v>
       </c>
-      <c r="P71" s="22">
+      <c r="P71" s="23">
         <v>-14.83</v>
       </c>
       <c r="Q71" s="20"/>
       <c r="R71" s="20"/>
-      <c r="S71" s="22">
+      <c r="S71" s="23">
         <v>-53.87</v>
       </c>
-      <c r="T71" s="22">
+      <c r="T71" s="23">
         <v>-43.89</v>
       </c>
-      <c r="U71" s="22">
+      <c r="U71" s="23">
         <v>-32.97</v>
       </c>
-      <c r="V71" s="22">
+      <c r="V71" s="23">
         <v>-5.9</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -18486,7 +18495,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="16">
@@ -19471,7 +19480,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19958,7 +19967,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20047,2403 +20056,2403 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" s="32">
         <v>46047.71</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>35499.02</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>26620.93</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>32803.86</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>25249.88</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>23075.58</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>16148.72</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>13299.79</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>10344.36</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>6465.52</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>5726.7</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>4970.83</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>2392.23</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>760.97</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>2343.17</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>1845.45</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>1781.88</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>2041.39</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>2090.1</v>
       </c>
-      <c r="U21" s="31"/>
+      <c r="U21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" s="32">
         <v>34170.37</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>29398.17</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>23962.9</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>21882.31</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>18699.18</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>13415.15</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>10324.59</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>8330.61</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>5904.14</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>4416.16</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>3377.97</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>2625.17</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>1824.51</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>1785.67</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>2031.72</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="B24" s="32">
         <v>29352.47</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>23674.57</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>18246.49</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>22653.83</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>15155.59</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>14616.74</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>8111.93</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>5821.56</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>4354.69</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>3106.26</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>2599.1</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>2374.56</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>623.67</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>576.99</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>1535.2</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>821.07</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>617.01</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>1040.65</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>1060.87</v>
       </c>
-      <c r="U24" s="31"/>
+      <c r="U24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="B25" s="32">
         <v>22457.07</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>19381.23</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>15258.3</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>13149.81</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>10196.61</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>6991.02</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>4762.6</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>3724.21</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>2564.22</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>2007.89</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>1609.15</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>1262.37</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>834.04</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>933.72</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>1020.46</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B27" s="33">
         <v>486.29</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>474.59</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>365.78</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>549.49</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>402.02</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>387.72</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>215.18</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>155.6</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>121.86</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>121.14</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>101.36</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>94.25</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>53.93</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>49.89</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>132.75</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>71.0</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>53.35</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>89.99</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>91.74</v>
       </c>
-      <c r="U27" s="31"/>
+      <c r="U27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="B28" s="33">
         <v>469.22</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>447.51</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>371.16</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>338.76</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>272.12</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>193.86</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>141.69</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>121.18</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>97.3</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>92.52</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>91.87</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>86.94</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>72.12</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>80.74</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>88.24</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="B30" s="35">
         <v>-5.16</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>-4.08</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>-1.83</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>-0.83</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>-1.55</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>-0.91</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>-4.28</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>-13.46</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-26.12</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>-11.14</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>-6.63</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>-6.18</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>-29.61</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>-6.18</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>4.16</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>15.52</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>-9.18</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-9.11</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>12.89</v>
       </c>
-      <c r="U30" s="35"/>
+      <c r="U30" s="36"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>347</v>
+      </c>
+      <c r="B31" s="35">
         <v>-2.69</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>-1.83</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>-1.57</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>-2.58</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>-5.66</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>-7.8</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>-11.55</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>-13.31</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>-15.27</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>-10.93</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <v>-6.06</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>-1.82</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <v>-1.84</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>0.25</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>3.48</v>
       </c>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="B33" s="36">
         <v>1.26</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>1.23</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>1.44</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>0.93</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>1.18</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>0.97</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>1.43</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>1.58</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>1.63</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>1.81</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>1.32</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>0.7</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>2.22</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>71.83</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>14.53</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>4.19</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>6.13</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>3.27</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.0</v>
       </c>
-      <c r="U33" s="35"/>
+      <c r="U33" s="36"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="B34" s="36">
         <v>1.19</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>1.13</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>1.15</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>1.12</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>1.25</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>1.34</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>1.54</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>1.45</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>1.5</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <v>10.61</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <v>13.99</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="36">
         <v>15.02</v>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="36">
         <v>17.16</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="36">
         <v>15.99</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>6.5</v>
       </c>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B35" s="36">
         <v>1.8</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>1.75</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>2.06</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>1.33</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>1.69</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>1.39</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>2.04</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>2.25</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>2.33</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>2.59</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>1.89</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>1.0</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>3.17</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>102.61</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>20.75</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>5.98</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>8.75</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>4.67</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>0.0</v>
       </c>
-      <c r="U35" s="35"/>
+      <c r="U35" s="36"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B36" s="36">
         <v>1.7</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>1.62</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>1.64</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>1.6</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>1.78</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>1.91</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>2.2</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>2.06</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>2.14</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>15.16</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>19.98</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>21.46</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>24.51</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>22.84</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>9.29</v>
       </c>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>352</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="B38" s="34">
         <v>1.24</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>1.36</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.16</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>2.07</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.91</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>2.47</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.57</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.27</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>1.18</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>1.2</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>1.37</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>1.54</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>1.0</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>2.24</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>2.09</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>1.15</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.86</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>1.23</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>1.41</v>
       </c>
-      <c r="U38" s="31"/>
+      <c r="U38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" s="34">
         <v>1.48</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.68</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.76</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.92</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.76</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.62</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>1.33</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>1.29</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>1.25</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>1.35</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>1.58</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>1.52</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>1.37</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>1.4</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>1.35</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="B41" s="34">
         <v>1.27</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.41</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.19</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>2.16</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>2.05</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>2.68</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>1.73</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>1.42</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>1.4</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>1.2</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>1.37</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>1.54</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>1.0</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>2.24</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>2.09</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>1.15</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.86</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>1.23</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>1.41</v>
       </c>
-      <c r="U41" s="31"/>
+      <c r="U41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B42" s="34">
         <v>1.54</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.76</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.87</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>2.07</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.94</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>1.78</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>1.44</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>1.38</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>1.3</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>1.35</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>1.58</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>1.52</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>1.37</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>1.4</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>1.35</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B44" s="34">
         <v>12.04</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>13.03</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>11.24</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>16.42</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>11.48</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>13.18</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>7.59</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>6.24</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>5.42</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>6.39</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>6.27</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>4.51</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>2.55</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>24.63</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>64.54</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>37.26</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>3.67</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>6.89</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>6.58</v>
       </c>
-      <c r="U44" s="31"/>
+      <c r="U44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>359</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B45" s="34">
         <v>12.83</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>13.07</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>12.11</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>11.35</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>9.14</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>8.13</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>6.44</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>5.72</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>4.86</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>5.25</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>7.0</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>8.55</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>8.74</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>11.94</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>9.79</v>
       </c>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>360</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="33">
+      <c r="A47" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="34">
         <v>24.03</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="34">
         <v>6.44</v>
       </c>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="33">
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="34">
         <v>7.76</v>
       </c>
-      <c r="U47" s="31"/>
+      <c r="U47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="32">
+      <c r="A48" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="33">
         <v>396.36</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="34">
         <v>28.71</v>
       </c>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" s="34">
         <v>24.37</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>23.81</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>8.69</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>8.46</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>9.49</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>12.72</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>10.04</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>8.76</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="34">
         <v>12.56</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="34">
         <v>5.19</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="34">
         <v>7.84</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="34">
         <v>10.32</v>
       </c>
-      <c r="N50" s="31"/>
-      <c r="O50" s="33">
+      <c r="N50" s="32"/>
+      <c r="O50" s="34">
         <v>10.76</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>18.8</v>
       </c>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="33">
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="34">
         <v>5.69</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>4.55</v>
       </c>
-      <c r="U50" s="31"/>
+      <c r="U50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B51" s="33">
+      <c r="A51" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="B51" s="34">
         <v>11.94</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>10.88</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>9.55</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>9.69</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>10.59</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>9.87</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>8.47</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>8.24</v>
       </c>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="33">
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="34">
         <v>24.13</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>14.1</v>
       </c>
-      <c r="Q51" s="31"/>
-      <c r="R51" s="31"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="B53" s="33">
+      <c r="A53" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="B53" s="34">
         <v>24.44</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>23.89</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>8.7</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>8.46</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>9.5</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>12.74</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>10.06</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>8.77</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="34">
         <v>12.59</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="34">
         <v>5.19</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>7.84</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>10.19</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>3.27</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>10.89</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>18.95</v>
       </c>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="33">
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="34">
         <v>5.72</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <v>4.57</v>
       </c>
-      <c r="U53" s="31"/>
+      <c r="U53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="B54" s="34">
         <v>11.95</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>10.89</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>9.56</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>9.7</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>10.61</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>9.88</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>8.48</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <v>8.23</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>6.84</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>6.3</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>8.57</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>11.37</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>21.77</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>24.77</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>14.3</v>
       </c>
-      <c r="Q54" s="31"/>
-      <c r="R54" s="31"/>
-      <c r="S54" s="31"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="B56" s="34">
         <v>26.03</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>31.07</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>28.7</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>133.08</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>43.07</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>38.65</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>18.03</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>13.83</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>15.35</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="34">
         <v>8.66</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>26.26</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>13.62</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>3.7</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>10.89</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>18.95</v>
       </c>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="33">
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="34">
         <v>6.93</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>4.57</v>
       </c>
-      <c r="U56" s="31"/>
+      <c r="U56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="B57" s="33">
+      <c r="A57" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B57" s="34">
         <v>1.48</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>1.68</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>1.76</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>1.92</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.76</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>1.62</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>1.33</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>1.29</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>1.25</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>1.35</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>1.58</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>1.52</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>1.37</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>1.4</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>1.35</v>
       </c>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="B59" s="37">
         <v>-12.7</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="37">
         <v>-0.43</v>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="37">
         <v>-0.26</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>0.13</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="34">
         <v>0.38</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>0.27</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>0.43</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>0.12</v>
       </c>
-      <c r="J59" s="36">
+      <c r="J59" s="37">
         <v>-0.23</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="34">
         <v>0.08</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>0.21</v>
       </c>
-      <c r="M59" s="36">
+      <c r="M59" s="37">
         <v>-0.21</v>
       </c>
-      <c r="N59" s="33">
+      <c r="N59" s="34">
         <v>0.01</v>
       </c>
-      <c r="O59" s="36">
+      <c r="O59" s="37">
         <v>-0.31</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>0.04</v>
       </c>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="36">
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="37">
         <v>-0.38</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.0</v>
       </c>
-      <c r="U59" s="31"/>
+      <c r="U59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="B60" s="37">
         <v>-1.22</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="37">
         <v>-5.22</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="34">
         <v>0.47</v>
       </c>
-      <c r="E60" s="33">
+      <c r="E60" s="34">
         <v>0.21</v>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="34">
         <v>0.84</v>
       </c>
-      <c r="G60" s="33">
+      <c r="G60" s="34">
         <v>0.51</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <v>0.49</v>
       </c>
-      <c r="I60" s="36">
+      <c r="I60" s="37">
         <v>-5.04</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="34">
         <v>0.49</v>
       </c>
-      <c r="K60" s="33">
+      <c r="K60" s="34">
         <v>0.28</v>
       </c>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-      <c r="N60" s="33">
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="34">
         <v>36.3</v>
       </c>
-      <c r="O60" s="36">
+      <c r="O60" s="37">
         <v>-1.0</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="34">
         <v>0.18</v>
       </c>
-      <c r="Q60" s="31"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="31"/>
-      <c r="T60" s="31"/>
-      <c r="U60" s="31"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B62" s="34">
         <v>20.42</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>19.5</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>18.32</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>24.27</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>19.13</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>20.8</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>15.17</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>14.9</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>13.87</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>13.31</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>13.85</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>16.65</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>9.76</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>32.49</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>98.5</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>83.74</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>10.59</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>13.51</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>12.97</v>
       </c>
-      <c r="U62" s="31"/>
+      <c r="U62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="B63" s="33">
+      <c r="A63" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B63" s="34">
         <v>20.28</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>20.32</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>19.68</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>19.31</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>17.17</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>16.2</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>14.43</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>14.4</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>13.62</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>13.83</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>16.19</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>20.34</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>19.13</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>22.83</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>19.49</v>
       </c>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="31"/>
-      <c r="T63" s="31"/>
-      <c r="U63" s="31"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="B65" s="34">
         <v>25.76</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>25.06</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>23.99</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>31.56</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>24.88</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>28.14</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>20.7</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>20.71</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>19.85</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>18.47</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>19.99</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>24.79</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>15.11</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>102.42</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>321.38</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>230.27</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="34">
         <v>13.75</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>17.2</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>17.58</v>
       </c>
-      <c r="U65" s="31"/>
+      <c r="U65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>380</v>
-      </c>
-      <c r="B66" s="33">
+      <c r="A66" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="34">
         <v>26.11</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>26.55</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>26.02</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>25.79</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>23.33</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>22.36</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>20.16</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>20.43</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>19.69</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>20.29</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>24.69</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="34">
         <v>32.8</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="34">
         <v>29.81</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="34">
         <v>32.8</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>26.87</v>
       </c>
-      <c r="Q66" s="31"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="31"/>
-      <c r="T66" s="31"/>
-      <c r="U66" s="31"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="32"/>
+      <c r="T66" s="32"/>
+      <c r="U66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B68" s="34">
         <v>34.8</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>33.2</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>22.79</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>41.5</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>32.49</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>40.1</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>31.96</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>32.91</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>37.68</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>22.13</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="34">
         <v>34.3</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>29.0</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>27.18</v>
       </c>
-      <c r="O68" s="31"/>
-      <c r="P68" s="33">
+      <c r="O68" s="32"/>
+      <c r="P68" s="34">
         <v>35.14</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>14.4</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>22.44</v>
       </c>
-      <c r="S68" s="32">
+      <c r="S68" s="33">
         <v>312.44</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>8.63</v>
       </c>
-      <c r="U68" s="31"/>
+      <c r="U68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B69" s="33">
+      <c r="A69" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B69" s="34">
         <v>32.3</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>32.65</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>32.41</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>36.33</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>34.85</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>34.0</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>31.78</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>31.33</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>30.29</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>30.13</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>35.39</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>28.89</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>27.36</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>34.94</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>19.57</v>
       </c>
-      <c r="Q69" s="31"/>
-      <c r="R69" s="31"/>
-      <c r="S69" s="31"/>
-      <c r="T69" s="31"/>
-      <c r="U69" s="31"/>
+      <c r="Q69" s="32"/>
+      <c r="R69" s="32"/>
+      <c r="S69" s="32"/>
+      <c r="T69" s="32"/>
+      <c r="U69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-      <c r="N71" s="31"/>
-      <c r="O71" s="31"/>
-      <c r="P71" s="33">
+      <c r="A71" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="34">
         <v>36.68</v>
       </c>
-      <c r="Q71" s="33">
+      <c r="Q71" s="34">
         <v>14.48</v>
       </c>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="33">
+      <c r="R71" s="32"/>
+      <c r="S71" s="32"/>
+      <c r="T71" s="34">
         <v>15.29</v>
       </c>
-      <c r="U71" s="31"/>
+      <c r="U71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-      <c r="N72" s="31"/>
-      <c r="O72" s="32">
+      <c r="A72" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
+      <c r="M72" s="32"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="33">
         <v>757.98</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="34">
         <v>57.16</v>
       </c>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="32"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/stx_xlsx/CATE.ST.xlsx
+++ b/data/stx_xlsx/CATE.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="390">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>Total Current Liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Deferred tax liability</t>
@@ -11593,8 +11596,8 @@
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="14" t="s">
-        <v>211</v>
+      <c r="A70" s="21" t="s">
+        <v>230</v>
       </c>
       <c r="B70" s="20">
         <v>16601.01</v>
@@ -11636,7 +11639,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="15">
         <v>3998.81</v>
@@ -11690,7 +11693,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="15">
         <v>300.7</v>
@@ -11732,7 +11735,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B73" s="16">
         <v>1.09</v>
@@ -11798,7 +11801,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -11850,7 +11853,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -11890,7 +11893,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -11930,7 +11933,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -11970,7 +11973,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -12000,7 +12003,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B79" s="22">
         <v>20901.62</v>
@@ -12068,7 +12071,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B80" s="22">
         <v>24959.47</v>
@@ -12136,7 +12139,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="15">
@@ -12202,7 +12205,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="20">
@@ -12268,7 +12271,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20">
@@ -12334,7 +12337,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="16">
@@ -12368,7 +12371,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -12406,7 +12409,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="22">
         <v>26212.58</v>
@@ -12474,7 +12477,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20">
@@ -12526,7 +12529,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B88" s="22"/>
       <c r="C88" s="22">
@@ -12578,7 +12581,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B89" s="22">
         <v>26212.58</v>
@@ -12646,7 +12649,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B90" s="22">
         <v>51172.05</v>
@@ -12714,7 +12717,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B91" s="16">
         <v>60.36</v>
@@ -12782,7 +12785,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B92" s="16">
         <v>60.36</v>
@@ -12850,7 +12853,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B93" s="20">
         <v>0.0</v>
@@ -12918,7 +12921,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B94" s="15">
         <v>487.57</v>
@@ -12958,7 +12961,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -12992,7 +12995,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -13050,7 +13053,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -13078,7 +13081,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -13110,7 +13113,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -13142,7 +13145,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -13172,7 +13175,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20">
@@ -13232,7 +13235,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="15">
@@ -13292,7 +13295,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="15">
@@ -13352,7 +13355,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="15">
@@ -13396,7 +13399,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="15">
@@ -13430,7 +13433,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="15">
@@ -13480,7 +13483,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -13508,7 +13511,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="15">
@@ -13544,7 +13547,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -13582,7 +13585,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -13620,7 +13623,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="15">
@@ -13658,7 +13661,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="16">
@@ -13708,7 +13711,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="16">
@@ -13758,7 +13761,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B114" s="16">
         <v>60.36</v>
@@ -13826,7 +13829,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B115" s="16">
         <v>60.36</v>
@@ -13894,7 +13897,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B116" s="20">
         <v>0.0</v>
@@ -13962,7 +13965,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B117" s="16">
         <v>1.0</v>
@@ -14030,7 +14033,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -14068,7 +14071,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -14106,7 +14109,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -14134,7 +14137,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B121" s="16">
         <v>74.0</v>
@@ -14202,7 +14205,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20">
@@ -14230,7 +14233,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -14282,7 +14285,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -14334,7 +14337,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -14386,7 +14389,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -14438,7 +14441,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="20">
@@ -15397,7 +15400,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15770,67 +15773,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15903,7 +15906,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15997,7 +16000,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B20" s="23">
         <v>-75.2</v>
@@ -16061,7 +16064,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -16089,7 +16092,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B22" s="15">
         <v>1640.64</v>
@@ -16139,7 +16142,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B23" s="15">
         <v>2189.29</v>
@@ -16207,7 +16210,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B24" s="24">
         <v>-473.45</v>
@@ -16265,7 +16268,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="23">
@@ -16311,7 +16314,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="16">
@@ -16361,7 +16364,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="24">
@@ -16413,7 +16416,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -16443,7 +16446,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="16">
@@ -16493,7 +16496,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="16">
@@ -16545,7 +16548,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="23">
@@ -16597,7 +16600,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -16633,7 +16636,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -16675,7 +16678,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -16705,7 +16708,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" s="16">
         <v>65.67</v>
@@ -16773,7 +16776,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" s="23">
         <v>-37.07</v>
@@ -16871,7 +16874,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -16903,7 +16906,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -16935,7 +16938,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B40" s="18">
         <v>1669.24</v>
@@ -17003,7 +17006,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
@@ -17045,7 +17048,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" s="24">
         <v>-664.1</v>
@@ -17085,7 +17088,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -17133,7 +17136,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="24">
@@ -17171,7 +17174,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20">
@@ -17201,7 +17204,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B46" s="16">
         <v>77.32</v>
@@ -17235,7 +17238,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B47" s="24">
         <v>-1220.16</v>
@@ -17303,7 +17306,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20">
@@ -17355,7 +17358,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -17409,7 +17412,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B50" s="16">
         <v>41.31</v>
@@ -17459,7 +17462,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -17489,7 +17492,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -17531,7 +17534,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -17567,7 +17570,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -17597,7 +17600,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B55" s="27">
         <v>-1765.62</v>
@@ -17665,7 +17668,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B56" s="20">
         <v>0.0</v>
@@ -17695,7 +17698,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B57" s="15">
         <v>102.74</v>
@@ -17761,7 +17764,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B58" s="24">
         <v>-575.13</v>
@@ -17823,7 +17826,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="28">
@@ -17875,7 +17878,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -17947,7 +17950,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B62" s="27">
         <v>-472.39</v>
@@ -18013,7 +18016,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -18041,7 +18044,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -18069,7 +18072,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -18097,7 +18100,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B66" s="24">
         <v>-568.77</v>
@@ -18143,7 +18146,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B67" s="15">
         <v>1082.53</v>
@@ -18211,7 +18214,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B68" s="23">
         <v>-9.53</v>
@@ -18261,7 +18264,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B69" s="15">
         <v>485.5</v>
@@ -18329,7 +18332,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B70" s="27">
         <v>-578.3</v>
@@ -18397,7 +18400,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="24">
@@ -18459,7 +18462,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -18495,7 +18498,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="16">
@@ -19480,7 +19483,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19967,7 +19970,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20057,7 +20060,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="29" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -20082,7 +20085,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B21" s="32">
         <v>46047.71</v>
@@ -20145,7 +20148,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B22" s="32">
         <v>34170.37</v>
@@ -20200,7 +20203,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -20225,7 +20228,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B24" s="32">
         <v>29352.47</v>
@@ -20288,7 +20291,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B25" s="32">
         <v>22457.07</v>
@@ -20343,7 +20346,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="29" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -20368,7 +20371,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B27" s="33">
         <v>486.29</v>
@@ -20431,7 +20434,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B28" s="33">
         <v>469.22</v>
@@ -20486,7 +20489,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -20511,7 +20514,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B30" s="35">
         <v>-5.16</v>
@@ -20574,7 +20577,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B31" s="35">
         <v>-2.69</v>
@@ -20629,7 +20632,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -20654,7 +20657,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B33" s="36">
         <v>1.26</v>
@@ -20717,7 +20720,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36">
         <v>1.19</v>
@@ -20772,7 +20775,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B35" s="36">
         <v>1.8</v>
@@ -20835,7 +20838,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B36" s="36">
         <v>1.7</v>
@@ -20890,7 +20893,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -20915,7 +20918,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B38" s="34">
         <v>1.24</v>
@@ -20978,7 +20981,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B39" s="34">
         <v>1.48</v>
@@ -21033,7 +21036,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -21058,7 +21061,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" s="34">
         <v>1.27</v>
@@ -21121,7 +21124,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" s="34">
         <v>1.54</v>
@@ -21176,7 +21179,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -21201,7 +21204,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" s="34">
         <v>12.04</v>
@@ -21264,7 +21267,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B45" s="34">
         <v>12.83</v>
@@ -21319,7 +21322,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="29" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -21344,7 +21347,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="31" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" s="32"/>
       <c r="C47" s="32"/>
@@ -21375,7 +21378,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="31" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" s="32"/>
       <c r="C48" s="32"/>
@@ -21404,7 +21407,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
@@ -21429,7 +21432,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="31" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B50" s="34">
         <v>24.37</v>
@@ -21486,7 +21489,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" s="34">
         <v>11.94</v>
@@ -21531,7 +21534,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
@@ -21556,7 +21559,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="31" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" s="34">
         <v>24.44</v>
@@ -21615,7 +21618,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B54" s="34">
         <v>11.95</v>
@@ -21670,7 +21673,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
@@ -21695,7 +21698,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B56" s="34">
         <v>26.03</v>
@@ -21754,7 +21757,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="31" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B57" s="34">
         <v>1.48</v>
@@ -21809,7 +21812,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
@@ -21834,7 +21837,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="31" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B59" s="37">
         <v>-12.7</v>
@@ -21893,7 +21896,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="31" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B60" s="37">
         <v>-1.22</v>
@@ -21944,7 +21947,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="29" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -21969,7 +21972,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="31" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B62" s="34">
         <v>20.42</v>
@@ -22032,7 +22035,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="31" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B63" s="34">
         <v>20.28</v>
@@ -22087,7 +22090,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B64" s="30"/>
       <c r="C64" s="30"/>
@@ -22112,7 +22115,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="31" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B65" s="34">
         <v>25.76</v>
@@ -22175,7 +22178,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="31" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B66" s="34">
         <v>26.11</v>
@@ -22230,7 +22233,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B67" s="30"/>
       <c r="C67" s="30"/>
@@ -22255,7 +22258,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="31" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B68" s="34">
         <v>34.8</v>
@@ -22316,7 +22319,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="31" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B69" s="34">
         <v>32.3</v>
@@ -22371,7 +22374,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="29" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B70" s="30"/>
       <c r="C70" s="30"/>
@@ -22396,7 +22399,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="32"/>
@@ -22427,7 +22430,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B72" s="32"/>
       <c r="C72" s="32"/>
